--- a/files/move_target.xlsx
+++ b/files/move_target.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E3FA15B-D107-4B96-804E-D7F8C9F8B6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56276827-C12A-4186-BCA7-2799A462B383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{11CD2EDA-407D-469C-B821-3A53E54AA7A7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{64E1A5C3-64C4-4932-B0C6-D08AE1363925}"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" r:id="rId1"/>
@@ -60,10 +60,10 @@
     <t>結果 (自己填)</t>
   </si>
   <si>
-    <t>同時打開這個檔案和同資料夾的「來源_報表.xlsx」，回到這個檔案，執行選單「資料搬移」</t>
-  </si>
-  <si>
-    <t>跳出「資料搬移」視窗；目標是「目標_底稿.xlsx」，來源自動選「來源_報表.xlsx」</t>
+    <t>同時打開這個檔案和同資料夾的「來源_報表.xlsx」，回到這個檔案，執行選單「整表匯入」</t>
+  </si>
+  <si>
+    <t>跳出「整表匯入」視窗；目標是「目標_底稿.xlsx」，來源自動選「來源_報表.xlsx」</t>
   </si>
   <si>
     <t>看工作表清單</t>
@@ -75,13 +75,13 @@
     <t>取消勾選 [說明] → [說明]</t>
   </si>
   <si>
-    <t>按鈕變成「開始搬移 (2 張)」</t>
-  </si>
-  <si>
-    <t>按「開始搬移」</t>
-  </si>
-  <si>
-    <t>視窗關閉，顯示「搬移完成 2 張工作表：[損益表]、[明細]」；來源檔還開著</t>
+    <t>按鈕變成「開始匯入 (2 張)」</t>
+  </si>
+  <si>
+    <t>按「開始匯入」</t>
+  </si>
+  <si>
+    <t>視窗關閉，顯示「匯入完成 2 張工作表：[損益表]、[明細]」；來源檔還開著</t>
   </si>
   <si>
     <t>看「損益表」</t>
@@ -120,16 +120,16 @@
     <t>內容都沒變 (說明表沒被來源蓋掉)</t>
   </si>
   <si>
-    <t>再執行一次「資料搬移」</t>
+    <t>再執行一次「整表匯入」</t>
   </si>
   <si>
     <t>[說明] 預設不勾 (上次取消勾選的會記住)；按「取消」關閉</t>
   </si>
   <si>
-    <t>關閉「來源_報表.xlsx」，回到這個檔案執行「資料搬移」</t>
-  </si>
-  <si>
-    <t>來源是空的，紅字提示「請先開啟來源活頁簿…」，「開始搬移」不能按</t>
+    <t>關閉「來源_報表.xlsx」，回到這個檔案執行「整表匯入」</t>
+  </si>
+  <si>
+    <t>來源是空的，紅字提示「請先開啟來源活頁簿…」，「開始匯入」不能按</t>
   </si>
   <si>
     <t>開著視窗時，按「來源」的下拉箭頭</t>
@@ -525,7 +525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368F5B33-0C4F-4BBD-A22E-770E6C849915}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBE39EA0-BEC4-4B58-9FCB-E7956CAEC58E}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -701,7 +701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A727C7D9-685C-4EFB-987E-A68DC4C52557}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58774F75-7828-4A8C-8941-EA711E01885E}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -945,7 +945,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6035F3A3-2F5F-430E-BC43-336BD01A0ABD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27BAF8C-7ECB-4662-86AB-9A5386504759}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8FA9124-398C-49A1-BE77-547909A2970E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64550B2-5642-4FC9-B560-64CF6A7D1055}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1082,7 +1082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A71AE7A4-BA67-4CFD-9337-20887734470E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9788E363-6A90-4007-A17D-30AD5B9C019F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1098,7 +1098,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716A3E74-A02F-45DE-990A-02CAA79C4C71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC27060-6646-4181-8FA4-49BAC0073B1A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
